--- a/server/data/products.xlsx
+++ b/server/data/products.xlsx
@@ -602,7 +602,7 @@
         <v>Harry Potter inspired Sorting Hat model, recreated as a detailed collectible for fans.</v>
       </c>
       <c r="D7">
-        <v>250</v>
+        <v>350</v>
       </c>
       <c r="E7" t="str">
         <v>PLA</v>

--- a/server/data/products.xlsx
+++ b/server/data/products.xlsx
@@ -442,7 +442,7 @@
         <v>3D-printed replica of Thing from Wednesday, designed as a collectible desk artifact for fans of the series.</v>
       </c>
       <c r="D2">
-        <v>600</v>
+        <v>750</v>
       </c>
       <c r="E2" t="str">
         <v>PLA</v>
@@ -474,7 +474,7 @@
         <v>Stranger Things inspired bookmark themed around Max, made for readers who love the series.</v>
       </c>
       <c r="D3">
-        <v>180</v>
+        <v>220</v>
       </c>
       <c r="E3" t="str">
         <v>PLA</v>
@@ -506,7 +506,7 @@
         <v>Harry Potter inspired bookmark designed for fans who want a magical touch while reading.</v>
       </c>
       <c r="D4">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E4" t="str">
         <v>PLA</v>
@@ -538,7 +538,7 @@
         <v>Second Harry Potter inspired bookmark with a magical fandom theme, suitable for readers and collectors.</v>
       </c>
       <c r="D5">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="E5" t="str">
         <v>PLA</v>
@@ -570,7 +570,7 @@
         <v>3D-printed Golden Snitch inspired by Harry Potter, made as a collectible decorative artifact.</v>
       </c>
       <c r="D6">
-        <v>350</v>
+        <v>450</v>
       </c>
       <c r="E6" t="str">
         <v>PLA</v>
@@ -602,7 +602,7 @@
         <v>Harry Potter inspired Sorting Hat model, recreated as a detailed collectible for fans.</v>
       </c>
       <c r="D7">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="E7" t="str">
         <v>PLA</v>
@@ -634,7 +634,7 @@
         <v>Harry Potter inspired Nimbus 2000 miniature, created as a decorative collectible prop.</v>
       </c>
       <c r="D8">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="E8" t="str">
         <v>PLA</v>
@@ -666,7 +666,7 @@
         <v>Stranger Things inspired Demadog figure, made as a detailed collectible for fans of the Upside Down.</v>
       </c>
       <c r="D9">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="E9" t="str">
         <v>PLA</v>
@@ -698,7 +698,7 @@
         <v>Harry Potter inspired decorative frame featuring the Deathly Hallows symbol.</v>
       </c>
       <c r="D10">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="E10" t="str">
         <v>PLA</v>
@@ -730,7 +730,7 @@
         <v>Game of Thrones inspired Iron Throne model, recreated as a collectible display artifact.</v>
       </c>
       <c r="D11">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="E11" t="str">
         <v>PLA</v>
@@ -762,7 +762,7 @@
         <v>Harry Potter inspired book page holder with Golden Snitch theme, designed for readers and collectors.</v>
       </c>
       <c r="D12">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="E12" t="str">
         <v>PLA</v>
@@ -794,7 +794,7 @@
         <v>Marvel inspired Groot figure, made as a decorative collectible for superhero fans.</v>
       </c>
       <c r="D13">
-        <v>450</v>
+        <v>550</v>
       </c>
       <c r="E13" t="str">
         <v>PLA</v>

--- a/server/data/products.xlsx
+++ b/server/data/products.xlsx
@@ -439,10 +439,10 @@
         <v>Thing Hand</v>
       </c>
       <c r="C2" t="str">
-        <v>3D-printed replica of Thing from Wednesday, designed as a collectible desk artifact for fans of the series.</v>
+        <v>3D-printed replica of Thing Hand, designed as a collectible desk artifact for fans of the series.</v>
       </c>
       <c r="D2">
-        <v>750</v>
+        <v>600</v>
       </c>
       <c r="E2" t="str">
         <v>PLA</v>
@@ -460,7 +460,7 @@
         <v>10cm x 8cm x 6cm</v>
       </c>
       <c r="J2" t="str">
-        <v>90g</v>
+        <v>81g</v>
       </c>
     </row>
     <row r="3">
@@ -471,10 +471,10 @@
         <v>Max Bookmark</v>
       </c>
       <c r="C3" t="str">
-        <v>Stranger Things inspired bookmark themed around Max, made for readers who love the series.</v>
+        <v>Bookmark themed around Max, made for readers who love the series.</v>
       </c>
       <c r="D3">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="E3" t="str">
         <v>PLA</v>
@@ -492,7 +492,7 @@
         <v>15cm x 4cm x 0.3cm</v>
       </c>
       <c r="J3" t="str">
-        <v>12g</v>
+        <v>13g</v>
       </c>
     </row>
     <row r="4">
@@ -500,10 +500,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>Harry Potter Bookmark 1</v>
+        <v>Disney Bookmark</v>
       </c>
       <c r="C4" t="str">
-        <v>Harry Potter inspired bookmark designed for fans who want a magical touch while reading.</v>
+        <v>Magical bookmark designed for fans who want a whimsical touch while reading.</v>
       </c>
       <c r="D4">
         <v>200</v>
@@ -521,10 +521,10 @@
         <v>/products/hp-bm1/hp-bm1.JPG</v>
       </c>
       <c r="I4" t="str">
-        <v>15cm x 4cm x 0.3cm</v>
+        <v>(16 x 5 x 0.2) cm</v>
       </c>
       <c r="J4" t="str">
-        <v>12g</v>
+        <v>8.33g</v>
       </c>
     </row>
     <row r="5">
@@ -532,10 +532,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v>Harry Potter Bookmark 2</v>
+        <v>Hogwarts Bookmark</v>
       </c>
       <c r="C5" t="str">
-        <v>Second Harry Potter inspired bookmark with a magical fandom theme, suitable for readers and collectors.</v>
+        <v>Hogwarts-themed bookmark with a magical fandom theme, suitable for readers and collectors.</v>
       </c>
       <c r="D5">
         <v>150</v>
@@ -544,7 +544,7 @@
         <v>PLA</v>
       </c>
       <c r="F5" t="str">
-        <v>Bookmark for books and a collectible add-on for Harry Potter fans.</v>
+        <v>Bookmark for books and a collectible add-on for fans.</v>
       </c>
       <c r="G5" t="str">
         <v>Bookmarks</v>
@@ -556,7 +556,7 @@
         <v>15cm x 4cm x 0.3cm</v>
       </c>
       <c r="J5" t="str">
-        <v>12g</v>
+        <v>9g</v>
       </c>
     </row>
     <row r="6">
@@ -567,10 +567,10 @@
         <v>Golden Snitch</v>
       </c>
       <c r="C6" t="str">
-        <v>3D-printed Golden Snitch inspired by Harry Potter, made as a collectible decorative artifact.</v>
+        <v>3D-printed Golden Snitch made as a collectible decorative artifact.</v>
       </c>
       <c r="D6">
-        <v>450</v>
+        <v>350</v>
       </c>
       <c r="E6" t="str">
         <v>PLA</v>
@@ -585,10 +585,10 @@
         <v>/products/snitch-ball/snitch-ball.JPG</v>
       </c>
       <c r="I6" t="str">
-        <v>8cm x 12cm x 8cm</v>
+        <v>(5 x 25 x 5) cm</v>
       </c>
       <c r="J6" t="str">
-        <v>35g</v>
+        <v>38g</v>
       </c>
     </row>
     <row r="7">
@@ -599,10 +599,10 @@
         <v>Sorting Hat</v>
       </c>
       <c r="C7" t="str">
-        <v>Harry Potter inspired Sorting Hat model, recreated as a detailed collectible for fans.</v>
+        <v>Sorting Hat model, recreated as a detailed collectible for fans.</v>
       </c>
       <c r="D7">
-        <v>500</v>
+        <v>350</v>
       </c>
       <c r="E7" t="str">
         <v>PLA</v>
@@ -617,10 +617,10 @@
         <v>/products/sorting-hat/sorting-hat.JPG</v>
       </c>
       <c r="I7" t="str">
-        <v>11cm x 11cm x 9cm</v>
+        <v>(7 x 8 x 8) cm</v>
       </c>
       <c r="J7" t="str">
-        <v>85g</v>
+        <v>35g</v>
       </c>
     </row>
     <row r="8">
@@ -631,10 +631,10 @@
         <v>Nimbus 2000</v>
       </c>
       <c r="C8" t="str">
-        <v>Harry Potter inspired Nimbus 2000 miniature, created as a decorative collectible prop.</v>
+        <v>Nimbus 2000 miniature, created as a decorative collectible prop.</v>
       </c>
       <c r="D8">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="E8" t="str">
         <v>PLA</v>
@@ -649,10 +649,10 @@
         <v>/products/nimbus/nimbus.JPG</v>
       </c>
       <c r="I8" t="str">
-        <v>20cm x 3cm x 4cm</v>
+        <v>(30 x 5 x 15) cm</v>
       </c>
       <c r="J8" t="str">
-        <v>40g</v>
+        <v>125g</v>
       </c>
     </row>
     <row r="9">
@@ -663,10 +663,10 @@
         <v>Demadog</v>
       </c>
       <c r="C9" t="str">
-        <v>Stranger Things inspired Demadog figure, made as a detailed collectible for fans of the Upside Down.</v>
+        <v>Demadog figure, made as a detailed collectible for fans of the Upside Down.</v>
       </c>
       <c r="D9">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="E9" t="str">
         <v>PLA</v>
@@ -684,7 +684,7 @@
         <v>14cm x 8cm x 7cm</v>
       </c>
       <c r="J9" t="str">
-        <v>95g</v>
+        <v>44g</v>
       </c>
     </row>
     <row r="10">
@@ -692,13 +692,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="str">
-        <v>Deathly Hallows Frame</v>
+        <v>Deathly Hallows Wall Hanging</v>
       </c>
       <c r="C10" t="str">
-        <v>Harry Potter inspired decorative frame featuring the Deathly Hallows symbol.</v>
+        <v>Decorative frame featuring the Deathly Hallows symbol.</v>
       </c>
       <c r="D10">
-        <v>350</v>
+        <v>150</v>
       </c>
       <c r="E10" t="str">
         <v>PLA</v>
@@ -713,10 +713,10 @@
         <v>/products/wall-hanging/wall-hanging.JPG</v>
       </c>
       <c r="I10" t="str">
-        <v>18cm x 18cm x 1.5cm</v>
+        <v>(5 x 5 x 6) cm</v>
       </c>
       <c r="J10" t="str">
-        <v>120g</v>
+        <v>12g</v>
       </c>
     </row>
     <row r="11">
@@ -727,10 +727,10 @@
         <v>Iron Throne</v>
       </c>
       <c r="C11" t="str">
-        <v>Game of Thrones inspired Iron Throne model, recreated as a collectible display artifact.</v>
+        <v>Iron Throne model, recreated as a collectible display artifact.</v>
       </c>
       <c r="D11">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="E11" t="str">
         <v>PLA</v>
@@ -748,7 +748,7 @@
         <v>16cm x 10cm x 8cm</v>
       </c>
       <c r="J11" t="str">
-        <v>150g</v>
+        <v>120g</v>
       </c>
     </row>
     <row r="12">
@@ -759,10 +759,10 @@
         <v>Golden Snitch Book Page Holder</v>
       </c>
       <c r="C12" t="str">
-        <v>Harry Potter inspired book page holder with Golden Snitch theme, designed for readers and collectors.</v>
+        <v>Book page holder, designed for readers and collectors.</v>
       </c>
       <c r="D12">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="E12" t="str">
         <v>PLA</v>
@@ -777,10 +777,10 @@
         <v>/products/snitch-bh/snitch-bh.JPG</v>
       </c>
       <c r="I12" t="str">
-        <v>7cm x 7cm x 2cm</v>
+        <v>(15 x 3 x 1) cm</v>
       </c>
       <c r="J12" t="str">
-        <v>25g</v>
+        <v>12.8g</v>
       </c>
     </row>
     <row r="13">
@@ -791,16 +791,16 @@
         <v>Groot</v>
       </c>
       <c r="C13" t="str">
-        <v>Marvel inspired Groot figure, made as a decorative collectible for superhero fans.</v>
+        <v>Groot figure, made as a decorative collectible for superhero fans.</v>
       </c>
       <c r="D13">
-        <v>550</v>
+        <v>450</v>
       </c>
       <c r="E13" t="str">
         <v>PLA</v>
       </c>
       <c r="F13" t="str">
-        <v>Display on desks, shelves, or gift to Marvel fans.</v>
+        <v>Display on desks, shelves, or gift to fans.</v>
       </c>
       <c r="G13" t="str">
         <v>Collectibles</v>
@@ -812,7 +812,7 @@
         <v>12cm x 7cm x 7cm</v>
       </c>
       <c r="J13" t="str">
-        <v>80g</v>
+        <v>52g</v>
       </c>
     </row>
   </sheetData>

--- a/server/data/products.xlsx
+++ b/server/data/products.xlsx
@@ -1,41 +1,296 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mayur\Desktop\WhoAmI\WhoAmI_Website\server\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2A6F21A-3A2D-4B17-B694-0A31963851A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Products" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="88">
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Price</t>
+  </si>
+  <si>
+    <t>Material</t>
+  </si>
+  <si>
+    <t>UseCase</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>ImageURL</t>
+  </si>
+  <si>
+    <t>Dimensions</t>
+  </si>
+  <si>
+    <t>Weight</t>
+  </si>
+  <si>
+    <t>Thing Hand</t>
+  </si>
+  <si>
+    <t>3D-printed replica of Thing Hand, designed as a collectible desk artifact for fans of the series.</t>
+  </si>
+  <si>
+    <t>PLA</t>
+  </si>
+  <si>
+    <t>Display on a desk, shelf, or fandom corner as a collectible prop.</t>
+  </si>
+  <si>
+    <t>Collectibles</t>
+  </si>
+  <si>
+    <t>/products/thing/thing.JPG</t>
+  </si>
+  <si>
+    <t>10cm x 8cm x 6cm</t>
+  </si>
+  <si>
+    <t>81g</t>
+  </si>
+  <si>
+    <t>Max Bookmark</t>
+  </si>
+  <si>
+    <t>Bookmark themed around Max, made for readers who love the series.</t>
+  </si>
+  <si>
+    <t>Bookmark for novels, journals, and fandom collections.</t>
+  </si>
+  <si>
+    <t>Bookmarks</t>
+  </si>
+  <si>
+    <t>/products/st-bm/st-bm.JPG</t>
+  </si>
+  <si>
+    <t>15cm x 4cm x 0.3cm</t>
+  </si>
+  <si>
+    <t>13g</t>
+  </si>
+  <si>
+    <t>Disney Bookmark</t>
+  </si>
+  <si>
+    <t>Magical bookmark designed for fans who want a whimsical touch while reading.</t>
+  </si>
+  <si>
+    <t>Use while reading books or keep as a collectible fandom accessory.</t>
+  </si>
+  <si>
+    <t>/products/hp-bm1/hp-bm1.JPG</t>
+  </si>
+  <si>
+    <t>(16 x 5 x 0.2) cm</t>
+  </si>
+  <si>
+    <t>8.33g</t>
+  </si>
+  <si>
+    <t>Hogwarts Bookmark</t>
+  </si>
+  <si>
+    <t>Hogwarts-themed bookmark with a magical fandom theme, suitable for readers and collectors.</t>
+  </si>
+  <si>
+    <t>Bookmark for books and a collectible add-on for fans.</t>
+  </si>
+  <si>
+    <t>/products/hp-bm2/hp-bm2.JPG</t>
+  </si>
+  <si>
+    <t>9g</t>
+  </si>
+  <si>
+    <t>Golden Snitch</t>
+  </si>
+  <si>
+    <t>3D-printed Golden Snitch made as a collectible decorative artifact.</t>
+  </si>
+  <si>
+    <t>Display piece for shelves, desks, and fandom setups.</t>
+  </si>
+  <si>
+    <t>/products/snitch-ball/snitch-ball.JPG</t>
+  </si>
+  <si>
+    <t>(5 x 25 x 5) cm</t>
+  </si>
+  <si>
+    <t>38g</t>
+  </si>
+  <si>
+    <t>Sorting Hat</t>
+  </si>
+  <si>
+    <t>Sorting Hat model, recreated as a detailed collectible for fans.</t>
+  </si>
+  <si>
+    <t>Decor item for desks, bookshelves, and fandom collections.</t>
+  </si>
+  <si>
+    <t>/products/sorting-hat/sorting-hat.JPG</t>
+  </si>
+  <si>
+    <t>(7 x 8 x 8) cm</t>
+  </si>
+  <si>
+    <t>35g</t>
+  </si>
+  <si>
+    <t>Nimbus 2000</t>
+  </si>
+  <si>
+    <t>Nimbus 2000 miniature, created as a decorative collectible prop.</t>
+  </si>
+  <si>
+    <t>Display as a miniature prop on desks, stands, or themed setups.</t>
+  </si>
+  <si>
+    <t>/products/nimbus/nimbus.JPG</t>
+  </si>
+  <si>
+    <t>(30 x 5 x 15) cm</t>
+  </si>
+  <si>
+    <t>125g</t>
+  </si>
+  <si>
+    <t>Demadog</t>
+  </si>
+  <si>
+    <t>Demadog figure, made as a detailed collectible for fans of the Upside Down.</t>
+  </si>
+  <si>
+    <t>Collectible display model for desks, shelves, and themed rooms.</t>
+  </si>
+  <si>
+    <t>/products/demadog/demadog.JPG</t>
+  </si>
+  <si>
+    <t>14cm x 8cm x 7cm</t>
+  </si>
+  <si>
+    <t>44g</t>
+  </si>
+  <si>
+    <t>Deathly Hallows Wall Hanging</t>
+  </si>
+  <si>
+    <t>Decorative frame featuring the Deathly Hallows symbol.</t>
+  </si>
+  <si>
+    <t>Wall or shelf decor piece for fandom spaces and personal collections.</t>
+  </si>
+  <si>
+    <t>Decor</t>
+  </si>
+  <si>
+    <t>/products/wall-hanging/wall-hanging.JPG</t>
+  </si>
+  <si>
+    <t>(5 x 5 x 6) cm</t>
+  </si>
+  <si>
+    <t>12g</t>
+  </si>
+  <si>
+    <t>Iron Throne</t>
+  </si>
+  <si>
+    <t>Iron Throne model, recreated as a collectible display artifact.</t>
+  </si>
+  <si>
+    <t>Premium collectible for desk display, shelf decor, or themed setups.</t>
+  </si>
+  <si>
+    <t>/products/throne/throne.JPG</t>
+  </si>
+  <si>
+    <t>16cm x 10cm x 8cm</t>
+  </si>
+  <si>
+    <t>120g</t>
+  </si>
+  <si>
+    <t>Golden Snitch Book Page Holder</t>
+  </si>
+  <si>
+    <t>Book page holder, designed for readers and collectors.</t>
+  </si>
+  <si>
+    <t>Hold book pages open while reading and serve as a fandom accessory.</t>
+  </si>
+  <si>
+    <t>Book Accessories</t>
+  </si>
+  <si>
+    <t>/products/snitch-bh/snitch-bh.JPG</t>
+  </si>
+  <si>
+    <t>(15 x 3 x 1) cm</t>
+  </si>
+  <si>
+    <t>12.8g</t>
+  </si>
+  <si>
+    <t>Groot</t>
+  </si>
+  <si>
+    <t>Groot figure, made as a decorative collectible for superhero fans.</t>
+  </si>
+  <si>
+    <t>Display on desks, shelves, or gift to fans.</t>
+  </si>
+  <si>
+    <t>/products/groot/groot.JPG</t>
+  </si>
+  <si>
+    <t>12cm x 7cm x 7cm</t>
+  </si>
+  <si>
+    <t>52g</t>
+  </si>
+  <si>
+    <t>OriginalPrice</t>
+  </si>
+  <si>
+    <t>Demagorgon Bookmark</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -72,6 +327,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,428 +659,501 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J13"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K14"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="18.09765625" customWidth="1"/>
+    <col min="3" max="3" width="15.19921875" customWidth="1"/>
+    <col min="7" max="7" width="20.796875" customWidth="1"/>
+    <col min="9" max="9" width="10.3984375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>ID</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Name</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Description</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Price</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Material</v>
-      </c>
-      <c r="F1" t="str">
-        <v>UseCase</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Category</v>
-      </c>
-      <c r="H1" t="str">
-        <v>ImageURL</v>
-      </c>
-      <c r="I1" t="str">
-        <v>Dimensions</v>
-      </c>
-      <c r="J1" t="str">
-        <v>Weight</v>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="str">
-        <v>Thing Hand</v>
-      </c>
-      <c r="C2" t="str">
-        <v>3D-printed replica of Thing Hand, designed as a collectible desk artifact for fans of the series.</v>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>11</v>
       </c>
       <c r="D2">
         <v>600</v>
       </c>
-      <c r="E2" t="str">
-        <v>PLA</v>
-      </c>
-      <c r="F2" t="str">
-        <v>Display on a desk, shelf, or fandom corner as a collectible prop.</v>
-      </c>
-      <c r="G2" t="str">
-        <v>Collectibles</v>
-      </c>
-      <c r="H2" t="str">
-        <v>/products/thing/thing.JPG</v>
-      </c>
-      <c r="I2" t="str">
-        <v>10cm x 8cm x 6cm</v>
-      </c>
-      <c r="J2" t="str">
-        <v>81g</v>
-      </c>
-    </row>
-    <row r="3">
+      <c r="E2">
+        <v>780</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="str">
-        <v>Max Bookmark</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Bookmark themed around Max, made for readers who love the series.</v>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" t="s">
+        <v>19</v>
       </c>
       <c r="D3">
         <v>200</v>
       </c>
-      <c r="E3" t="str">
-        <v>PLA</v>
-      </c>
-      <c r="F3" t="str">
-        <v>Bookmark for novels, journals, and fandom collections.</v>
-      </c>
-      <c r="G3" t="str">
-        <v>Bookmarks</v>
-      </c>
-      <c r="H3" t="str">
-        <v>/products/st-bm/st-bm.JPG</v>
-      </c>
-      <c r="I3" t="str">
-        <v>15cm x 4cm x 0.3cm</v>
-      </c>
-      <c r="J3" t="str">
-        <v>13g</v>
-      </c>
-    </row>
-    <row r="4">
+      <c r="E3">
+        <v>310</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="str">
-        <v>Disney Bookmark</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Magical bookmark designed for fans who want a whimsical touch while reading.</v>
+      <c r="B4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" t="s">
+        <v>26</v>
       </c>
       <c r="D4">
         <v>200</v>
       </c>
-      <c r="E4" t="str">
-        <v>PLA</v>
-      </c>
-      <c r="F4" t="str">
-        <v>Use while reading books or keep as a collectible fandom accessory.</v>
-      </c>
-      <c r="G4" t="str">
-        <v>Bookmarks</v>
-      </c>
-      <c r="H4" t="str">
-        <v>/products/hp-bm1/hp-bm1.JPG</v>
-      </c>
-      <c r="I4" t="str">
-        <v>(16 x 5 x 0.2) cm</v>
-      </c>
-      <c r="J4" t="str">
-        <v>8.33g</v>
-      </c>
-    </row>
-    <row r="5">
+      <c r="E4">
+        <v>290</v>
+      </c>
+      <c r="F4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" t="s">
+        <v>28</v>
+      </c>
+      <c r="J4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="str">
-        <v>Hogwarts Bookmark</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Hogwarts-themed bookmark with a magical fandom theme, suitable for readers and collectors.</v>
+      <c r="B5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" t="s">
+        <v>32</v>
       </c>
       <c r="D5">
         <v>150</v>
       </c>
-      <c r="E5" t="str">
-        <v>PLA</v>
-      </c>
-      <c r="F5" t="str">
-        <v>Bookmark for books and a collectible add-on for fans.</v>
-      </c>
-      <c r="G5" t="str">
-        <v>Bookmarks</v>
-      </c>
-      <c r="H5" t="str">
-        <v>/products/hp-bm2/hp-bm2.JPG</v>
-      </c>
-      <c r="I5" t="str">
-        <v>15cm x 4cm x 0.3cm</v>
-      </c>
-      <c r="J5" t="str">
-        <v>9g</v>
-      </c>
-    </row>
-    <row r="6">
+      <c r="E5">
+        <v>210</v>
+      </c>
+      <c r="F5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" t="s">
+        <v>34</v>
+      </c>
+      <c r="J5" t="s">
+        <v>23</v>
+      </c>
+      <c r="K5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" t="str">
-        <v>Golden Snitch</v>
-      </c>
-      <c r="C6" t="str">
-        <v>3D-printed Golden Snitch made as a collectible decorative artifact.</v>
+      <c r="B6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" t="s">
+        <v>37</v>
       </c>
       <c r="D6">
         <v>350</v>
       </c>
-      <c r="E6" t="str">
-        <v>PLA</v>
-      </c>
-      <c r="F6" t="str">
-        <v>Display piece for shelves, desks, and fandom setups.</v>
-      </c>
-      <c r="G6" t="str">
-        <v>Collectibles</v>
-      </c>
-      <c r="H6" t="str">
-        <v>/products/snitch-ball/snitch-ball.JPG</v>
-      </c>
-      <c r="I6" t="str">
-        <v>(5 x 25 x 5) cm</v>
-      </c>
-      <c r="J6" t="str">
-        <v>38g</v>
-      </c>
-    </row>
-    <row r="7">
+      <c r="E6">
+        <v>425</v>
+      </c>
+      <c r="F6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I6" t="s">
+        <v>39</v>
+      </c>
+      <c r="J6" t="s">
+        <v>40</v>
+      </c>
+      <c r="K6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" t="str">
-        <v>Sorting Hat</v>
-      </c>
-      <c r="C7" t="str">
-        <v>Sorting Hat model, recreated as a detailed collectible for fans.</v>
+      <c r="B7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" t="s">
+        <v>43</v>
       </c>
       <c r="D7">
         <v>350</v>
       </c>
-      <c r="E7" t="str">
-        <v>PLA</v>
-      </c>
-      <c r="F7" t="str">
-        <v>Decor item for desks, bookshelves, and fandom collections.</v>
-      </c>
-      <c r="G7" t="str">
-        <v>Collectibles</v>
-      </c>
-      <c r="H7" t="str">
-        <v>/products/sorting-hat/sorting-hat.JPG</v>
-      </c>
-      <c r="I7" t="str">
-        <v>(7 x 8 x 8) cm</v>
-      </c>
-      <c r="J7" t="str">
-        <v>35g</v>
-      </c>
-    </row>
-    <row r="8">
+      <c r="E7">
+        <v>450</v>
+      </c>
+      <c r="F7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" t="s">
+        <v>44</v>
+      </c>
+      <c r="H7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I7" t="s">
+        <v>45</v>
+      </c>
+      <c r="J7" t="s">
+        <v>46</v>
+      </c>
+      <c r="K7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" t="str">
-        <v>Nimbus 2000</v>
-      </c>
-      <c r="C8" t="str">
-        <v>Nimbus 2000 miniature, created as a decorative collectible prop.</v>
+      <c r="B8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" t="s">
+        <v>49</v>
       </c>
       <c r="D8">
         <v>900</v>
       </c>
-      <c r="E8" t="str">
-        <v>PLA</v>
-      </c>
-      <c r="F8" t="str">
-        <v>Display as a miniature prop on desks, stands, or themed setups.</v>
-      </c>
-      <c r="G8" t="str">
-        <v>Collectibles</v>
-      </c>
-      <c r="H8" t="str">
-        <v>/products/nimbus/nimbus.JPG</v>
-      </c>
-      <c r="I8" t="str">
-        <v>(30 x 5 x 15) cm</v>
-      </c>
-      <c r="J8" t="str">
-        <v>125g</v>
-      </c>
-    </row>
-    <row r="9">
+      <c r="E8">
+        <v>1220</v>
+      </c>
+      <c r="F8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" t="s">
+        <v>50</v>
+      </c>
+      <c r="H8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I8" t="s">
+        <v>51</v>
+      </c>
+      <c r="J8" t="s">
+        <v>52</v>
+      </c>
+      <c r="K8" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" t="str">
-        <v>Demadog</v>
-      </c>
-      <c r="C9" t="str">
-        <v>Demadog figure, made as a detailed collectible for fans of the Upside Down.</v>
+      <c r="B9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" t="s">
+        <v>55</v>
       </c>
       <c r="D9">
         <v>450</v>
       </c>
-      <c r="E9" t="str">
-        <v>PLA</v>
-      </c>
-      <c r="F9" t="str">
-        <v>Collectible display model for desks, shelves, and themed rooms.</v>
-      </c>
-      <c r="G9" t="str">
-        <v>Collectibles</v>
-      </c>
-      <c r="H9" t="str">
-        <v>/products/demadog/demadog.JPG</v>
-      </c>
-      <c r="I9" t="str">
-        <v>14cm x 8cm x 7cm</v>
-      </c>
-      <c r="J9" t="str">
-        <v>44g</v>
-      </c>
-    </row>
-    <row r="10">
+      <c r="E9">
+        <v>590</v>
+      </c>
+      <c r="F9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" t="s">
+        <v>56</v>
+      </c>
+      <c r="H9" t="s">
+        <v>14</v>
+      </c>
+      <c r="I9" t="s">
+        <v>57</v>
+      </c>
+      <c r="J9" t="s">
+        <v>58</v>
+      </c>
+      <c r="K9" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" t="str">
-        <v>Deathly Hallows Wall Hanging</v>
-      </c>
-      <c r="C10" t="str">
-        <v>Decorative frame featuring the Deathly Hallows symbol.</v>
+      <c r="B10" t="s">
+        <v>60</v>
+      </c>
+      <c r="C10" t="s">
+        <v>61</v>
       </c>
       <c r="D10">
         <v>150</v>
       </c>
-      <c r="E10" t="str">
-        <v>PLA</v>
-      </c>
-      <c r="F10" t="str">
-        <v>Wall or shelf decor piece for fandom spaces and personal collections.</v>
-      </c>
-      <c r="G10" t="str">
-        <v>Decor</v>
-      </c>
-      <c r="H10" t="str">
-        <v>/products/wall-hanging/wall-hanging.JPG</v>
-      </c>
-      <c r="I10" t="str">
-        <v>(5 x 5 x 6) cm</v>
-      </c>
-      <c r="J10" t="str">
-        <v>12g</v>
-      </c>
-    </row>
-    <row r="11">
+      <c r="E10">
+        <v>200</v>
+      </c>
+      <c r="F10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" t="s">
+        <v>62</v>
+      </c>
+      <c r="H10" t="s">
+        <v>63</v>
+      </c>
+      <c r="I10" t="s">
+        <v>64</v>
+      </c>
+      <c r="J10" t="s">
+        <v>65</v>
+      </c>
+      <c r="K10" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" t="str">
-        <v>Iron Throne</v>
-      </c>
-      <c r="C11" t="str">
-        <v>Iron Throne model, recreated as a collectible display artifact.</v>
+      <c r="B11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C11" t="s">
+        <v>68</v>
       </c>
       <c r="D11">
         <v>800</v>
       </c>
-      <c r="E11" t="str">
-        <v>PLA</v>
-      </c>
-      <c r="F11" t="str">
-        <v>Premium collectible for desk display, shelf decor, or themed setups.</v>
-      </c>
-      <c r="G11" t="str">
-        <v>Collectibles</v>
-      </c>
-      <c r="H11" t="str">
-        <v>/products/throne/throne.JPG</v>
-      </c>
-      <c r="I11" t="str">
-        <v>16cm x 10cm x 8cm</v>
-      </c>
-      <c r="J11" t="str">
-        <v>120g</v>
-      </c>
-    </row>
-    <row r="12">
+      <c r="E11">
+        <v>1040</v>
+      </c>
+      <c r="F11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" t="s">
+        <v>69</v>
+      </c>
+      <c r="H11" t="s">
+        <v>14</v>
+      </c>
+      <c r="I11" t="s">
+        <v>70</v>
+      </c>
+      <c r="J11" t="s">
+        <v>71</v>
+      </c>
+      <c r="K11" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" t="str">
-        <v>Golden Snitch Book Page Holder</v>
-      </c>
-      <c r="C12" t="str">
-        <v>Book page holder, designed for readers and collectors.</v>
+      <c r="B12" t="s">
+        <v>73</v>
+      </c>
+      <c r="C12" t="s">
+        <v>74</v>
       </c>
       <c r="D12">
         <v>200</v>
       </c>
-      <c r="E12" t="str">
-        <v>PLA</v>
-      </c>
-      <c r="F12" t="str">
-        <v>Hold book pages open while reading and serve as a fandom accessory.</v>
-      </c>
-      <c r="G12" t="str">
-        <v>Book Accessories</v>
-      </c>
-      <c r="H12" t="str">
-        <v>/products/snitch-bh/snitch-bh.JPG</v>
-      </c>
-      <c r="I12" t="str">
-        <v>(15 x 3 x 1) cm</v>
-      </c>
-      <c r="J12" t="str">
-        <v>12.8g</v>
-      </c>
-    </row>
-    <row r="13">
+      <c r="E12">
+        <v>350</v>
+      </c>
+      <c r="F12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" t="s">
+        <v>75</v>
+      </c>
+      <c r="H12" t="s">
+        <v>76</v>
+      </c>
+      <c r="I12" t="s">
+        <v>77</v>
+      </c>
+      <c r="J12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K12" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" t="str">
-        <v>Groot</v>
-      </c>
-      <c r="C13" t="str">
-        <v>Groot figure, made as a decorative collectible for superhero fans.</v>
+      <c r="B13" t="s">
+        <v>80</v>
+      </c>
+      <c r="C13" t="s">
+        <v>81</v>
       </c>
       <c r="D13">
         <v>450</v>
       </c>
-      <c r="E13" t="str">
-        <v>PLA</v>
-      </c>
-      <c r="F13" t="str">
-        <v>Display on desks, shelves, or gift to fans.</v>
-      </c>
-      <c r="G13" t="str">
-        <v>Collectibles</v>
-      </c>
-      <c r="H13" t="str">
-        <v>/products/groot/groot.JPG</v>
-      </c>
-      <c r="I13" t="str">
-        <v>12cm x 7cm x 7cm</v>
-      </c>
-      <c r="J13" t="str">
-        <v>52g</v>
+      <c r="E13">
+        <v>590</v>
+      </c>
+      <c r="F13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" t="s">
+        <v>82</v>
+      </c>
+      <c r="H13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I13" t="s">
+        <v>83</v>
+      </c>
+      <c r="J13" t="s">
+        <v>84</v>
+      </c>
+      <c r="K13" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>87</v>
+      </c>
+      <c r="C14" t="s">
+        <v>81</v>
+      </c>
+      <c r="D14">
+        <v>79</v>
+      </c>
+      <c r="E14">
+        <v>99</v>
+      </c>
+      <c r="F14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J13"/>
+    <ignoredError sqref="F1:K13 A1:D13" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>